--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_event_windows.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_event_windows.xlsx
@@ -471,7 +471,7 @@
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="13" customWidth="1" min="36" max="36"/>
     <col width="27" customWidth="1" min="37" max="37"/>
-    <col width="42" customWidth="1" min="38" max="38"/>
+    <col width="45" customWidth="1" min="38" max="38"/>
     <col width="17" customWidth="1" min="39" max="39"/>
     <col width="45" customWidth="1" min="40" max="40"/>
   </cols>
@@ -813,12 +813,12 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -967,12 +967,12 @@
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1121,12 +1121,12 @@
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1275,12 +1275,12 @@
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1429,12 +1429,12 @@
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1583,12 +1583,12 @@
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1737,12 +1737,12 @@
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1891,12 +1891,12 @@
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2045,12 +2045,12 @@
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -2199,12 +2199,12 @@
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2353,12 +2353,12 @@
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>0.5718111133827007</v>
+        <v>0.5718111133827006</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2507,12 +2507,12 @@
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2661,12 +2661,12 @@
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2815,12 +2815,12 @@
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2969,12 +2969,12 @@
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -3123,12 +3123,12 @@
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -3277,12 +3277,12 @@
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -3431,12 +3431,12 @@
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -3585,12 +3585,12 @@
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -3739,12 +3739,12 @@
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -3893,12 +3893,12 @@
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -4047,12 +4047,12 @@
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>0.5305974233139065</v>
+        <v>0.5305974233139066</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -4201,12 +4201,12 @@
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -4355,12 +4355,12 @@
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -4509,12 +4509,12 @@
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -4663,12 +4663,12 @@
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -4813,12 +4813,12 @@
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -4963,12 +4963,12 @@
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>0.5994345955998126</v>
+        <v>0.5994345955998127</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -5113,12 +5113,12 @@
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>0.5956150709355212</v>
+        <v>0.5956150709355211</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -5263,12 +5263,12 @@
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>0.6168504099184342</v>
+        <v>0.6168504099184341</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -5413,12 +5413,12 @@
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -5563,12 +5563,12 @@
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -5713,12 +5713,12 @@
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -5829,11 +5829,11 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>0.7019151795737005</v>
+        <v>0.6269151795737006</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5867,12 +5867,12 @@
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -5983,11 +5983,11 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>0.6939533714354214</v>
+        <v>0.6189533714354214</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -6021,12 +6021,12 @@
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -6137,11 +6137,11 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>0.683272773230519</v>
+        <v>0.6082727732305192</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -6175,12 +6175,12 @@
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -6291,11 +6291,11 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>0.6956379177840647</v>
+        <v>0.6206379177840649</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -6329,12 +6329,12 @@
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -6445,11 +6445,11 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>0.7296947020637291</v>
+        <v>0.6546947020637292</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -6483,12 +6483,12 @@
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -6599,11 +6599,11 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>0.7066022071362258</v>
+        <v>0.6316022071362259</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -6637,12 +6637,12 @@
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -6753,11 +6753,11 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>0.6495961916892383</v>
+        <v>0.6006831482109777</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -6791,12 +6791,12 @@
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -6907,11 +6907,11 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>0.6112263128261235</v>
+        <v>0.5656905985404093</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6945,12 +6945,12 @@
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -7099,12 +7099,12 @@
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -7215,11 +7215,11 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>0.6519756159724542</v>
+        <v>0.5769756159724543</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -7253,12 +7253,12 @@
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -7407,12 +7407,12 @@
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -7561,12 +7561,12 @@
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -7715,12 +7715,12 @@
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
@@ -7869,12 +7869,12 @@
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>0.5959377399571273</v>
+        <v>0.5959377399571272</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -8023,12 +8023,12 @@
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -8177,12 +8177,12 @@
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -8327,12 +8327,12 @@
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>0.5229508535828796</v>
+        <v>0.5229508535828795</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -8481,12 +8481,12 @@
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -8635,12 +8635,12 @@
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -8789,12 +8789,12 @@
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>0.6029854882484185</v>
+        <v>0.6029854882484182</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -8943,12 +8943,12 @@
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>0.5514346742145123</v>
+        <v>0.5514346742145122</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -9097,12 +9097,12 @@
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -9251,12 +9251,12 @@
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -9401,12 +9401,12 @@
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -9551,12 +9551,12 @@
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -9701,12 +9701,12 @@
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -9851,12 +9851,12 @@
       <c r="AJ61" t="inlineStr"/>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
@@ -10001,12 +10001,12 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
@@ -10151,12 +10151,12 @@
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
@@ -10301,12 +10301,12 @@
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
@@ -10451,12 +10451,12 @@
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
@@ -10601,12 +10601,12 @@
       <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
@@ -10751,12 +10751,12 @@
       <c r="AJ67" t="inlineStr"/>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
@@ -10863,7 +10863,7 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>0.6096047013538199</v>
+        <v>0.6096047013538198</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -10901,12 +10901,12 @@
       <c r="AJ68" t="inlineStr"/>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
@@ -11013,7 +11013,7 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>0.6080356447052087</v>
+        <v>0.6080356447052085</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -11051,12 +11051,12 @@
       <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
@@ -11205,12 +11205,12 @@
       <c r="AJ70" t="inlineStr"/>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -11359,12 +11359,12 @@
       <c r="AJ71" t="inlineStr"/>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -11513,12 +11513,12 @@
       <c r="AJ72" t="inlineStr"/>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -11667,12 +11667,12 @@
       <c r="AJ73" t="inlineStr"/>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -11821,12 +11821,12 @@
       <c r="AJ74" t="inlineStr"/>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
@@ -11975,12 +11975,12 @@
       <c r="AJ75" t="inlineStr"/>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -12129,12 +12129,12 @@
       <c r="AJ76" t="inlineStr"/>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
@@ -12283,12 +12283,12 @@
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -12437,12 +12437,12 @@
       <c r="AJ78" t="inlineStr"/>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -12591,12 +12591,12 @@
       <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -12745,12 +12745,12 @@
       <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
@@ -12899,12 +12899,12 @@
       <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -13053,12 +13053,12 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
@@ -13207,12 +13207,12 @@
       <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
@@ -13361,12 +13361,12 @@
       <c r="AJ84" t="inlineStr"/>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
@@ -13515,12 +13515,12 @@
       <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
@@ -13669,12 +13669,12 @@
       <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -13823,12 +13823,12 @@
       <c r="AJ87" t="inlineStr"/>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
@@ -13977,12 +13977,12 @@
       <c r="AJ88" t="inlineStr"/>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -14131,12 +14131,12 @@
       <c r="AJ89" t="inlineStr"/>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
@@ -14285,12 +14285,12 @@
       <c r="AJ90" t="inlineStr"/>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
@@ -14439,12 +14439,12 @@
       <c r="AJ91" t="inlineStr"/>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
@@ -14593,12 +14593,12 @@
       <c r="AJ92" t="inlineStr"/>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
@@ -14747,12 +14747,12 @@
       <c r="AJ93" t="inlineStr"/>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
@@ -14897,12 +14897,12 @@
       <c r="AJ94" t="inlineStr"/>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
@@ -15013,7 +15013,7 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>0.5385706286630147</v>
+        <v>0.5385706286630146</v>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
@@ -15051,12 +15051,12 @@
       <c r="AJ95" t="inlineStr"/>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -15205,12 +15205,12 @@
       <c r="AJ96" t="inlineStr"/>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
@@ -15359,12 +15359,12 @@
       <c r="AJ97" t="inlineStr"/>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
@@ -15513,12 +15513,12 @@
       <c r="AJ98" t="inlineStr"/>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
@@ -15667,12 +15667,12 @@
       <c r="AJ99" t="inlineStr"/>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
@@ -15821,12 +15821,12 @@
       <c r="AJ100" t="inlineStr"/>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
@@ -15975,12 +15975,12 @@
       <c r="AJ101" t="inlineStr"/>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
@@ -16125,12 +16125,12 @@
       <c r="AJ102" t="inlineStr"/>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
@@ -16275,12 +16275,12 @@
       <c r="AJ103" t="inlineStr"/>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>0.617531458479232</v>
+        <v>0.6175314584792321</v>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
@@ -16425,12 +16425,12 @@
       <c r="AJ104" t="inlineStr"/>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -16537,7 +16537,7 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>0.6181993886010698</v>
+        <v>0.6181993886010699</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
@@ -16575,12 +16575,12 @@
       <c r="AJ105" t="inlineStr"/>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>0.6111222315146568</v>
+        <v>0.6111222315146569</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
@@ -16725,12 +16725,12 @@
       <c r="AJ106" t="inlineStr"/>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
@@ -16875,12 +16875,12 @@
       <c r="AJ107" t="inlineStr"/>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
@@ -17025,12 +17025,12 @@
       <c r="AJ108" t="inlineStr"/>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
@@ -17175,12 +17175,12 @@
       <c r="AJ109" t="inlineStr"/>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
@@ -17325,12 +17325,12 @@
       <c r="AJ110" t="inlineStr"/>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
@@ -17475,12 +17475,12 @@
       <c r="AJ111" t="inlineStr"/>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
@@ -17625,12 +17625,12 @@
       <c r="AJ112" t="inlineStr"/>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -17775,12 +17775,12 @@
       <c r="AJ113" t="inlineStr"/>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -17925,12 +17925,12 @@
       <c r="AJ114" t="inlineStr"/>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -18075,12 +18075,12 @@
       <c r="AJ115" t="inlineStr"/>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -18225,12 +18225,12 @@
       <c r="AJ116" t="inlineStr"/>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -18341,11 +18341,11 @@
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>0.7009432034667815</v>
+        <v>0.6259432034667817</v>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
@@ -18379,12 +18379,12 @@
       <c r="AJ117" t="inlineStr"/>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -18495,11 +18495,11 @@
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>0.6809900465594697</v>
+        <v>0.60599004655947</v>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
@@ -18533,12 +18533,12 @@
       <c r="AJ118" t="inlineStr"/>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -18649,11 +18649,11 @@
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>0.7075817199296366</v>
+        <v>0.6325817199296366</v>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
@@ -18687,12 +18687,12 @@
       <c r="AJ119" t="inlineStr"/>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
@@ -18803,11 +18803,11 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>0.7025100033632101</v>
+        <v>0.6275100033632102</v>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
@@ -18841,12 +18841,12 @@
       <c r="AJ120" t="inlineStr"/>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -18957,11 +18957,11 @@
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>0.7237271969005055</v>
+        <v>0.6487271969005055</v>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
@@ -18995,12 +18995,12 @@
       <c r="AJ121" t="inlineStr"/>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -19111,11 +19111,11 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>0.6700299642641597</v>
+        <v>0.5950299642641599</v>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
@@ -19149,12 +19149,12 @@
       <c r="AJ122" t="inlineStr"/>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -19265,11 +19265,11 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>0.7001734700020641</v>
+        <v>0.6251734700020641</v>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
@@ -19303,12 +19303,12 @@
       <c r="AJ123" t="inlineStr"/>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
@@ -19419,11 +19419,11 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>0.6830672184134324</v>
+        <v>0.6080672184134325</v>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
@@ -19457,12 +19457,12 @@
       <c r="AJ124" t="inlineStr"/>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -19573,11 +19573,11 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>0.6220030356341557</v>
+        <v>0.5470030356341558</v>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
@@ -19611,12 +19611,12 @@
       <c r="AJ125" t="inlineStr"/>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
@@ -19727,11 +19727,11 @@
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>0.7111815812927388</v>
+        <v>0.6361815812927388</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
@@ -19765,12 +19765,12 @@
       <c r="AJ126" t="inlineStr"/>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
@@ -19881,11 +19881,11 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>0.7247527750181934</v>
+        <v>0.6497527750181935</v>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
@@ -19919,12 +19919,12 @@
       <c r="AJ127" t="inlineStr"/>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -20035,11 +20035,11 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>0.7213629077949615</v>
+        <v>0.6463629077949615</v>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
@@ -20073,12 +20073,12 @@
       <c r="AJ128" t="inlineStr"/>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -20189,11 +20189,11 @@
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>0.7361438266941112</v>
+        <v>0.6611438266941111</v>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
@@ -20227,12 +20227,12 @@
       <c r="AJ129" t="inlineStr"/>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -20343,11 +20343,11 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>0.7521009006810253</v>
+        <v>0.6771009006810254</v>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
@@ -20381,12 +20381,12 @@
       <c r="AJ130" t="inlineStr"/>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -20497,11 +20497,11 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>0.7272107579052537</v>
+        <v>0.6522107579052536</v>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
@@ -20535,12 +20535,12 @@
       <c r="AJ131" t="inlineStr"/>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
@@ -20651,11 +20651,11 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>0.7504841298589713</v>
+        <v>0.6754841298589712</v>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
@@ -20689,12 +20689,12 @@
       <c r="AJ132" t="inlineStr"/>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -20805,11 +20805,11 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>0.7041961268271593</v>
+        <v>0.6291961268271594</v>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
@@ -20843,12 +20843,12 @@
       <c r="AJ133" t="inlineStr"/>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
@@ -20959,11 +20959,11 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>0.7055250039544226</v>
+        <v>0.6305250039544227</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
@@ -20997,12 +20997,12 @@
       <c r="AJ134" t="inlineStr"/>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -21151,12 +21151,12 @@
       <c r="AJ135" t="inlineStr"/>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
@@ -21305,12 +21305,12 @@
       <c r="AJ136" t="inlineStr"/>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
@@ -21421,7 +21421,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>0.5931167224791165</v>
+        <v>0.5931167224791164</v>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
@@ -21459,12 +21459,12 @@
       <c r="AJ137" t="inlineStr"/>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
@@ -21575,7 +21575,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>0.59432603471926</v>
+        <v>0.5810907406016128</v>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
@@ -21613,12 +21613,12 @@
       <c r="AJ138" t="inlineStr"/>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM138" t="inlineStr">
@@ -21767,12 +21767,12 @@
       <c r="AJ139" t="inlineStr"/>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL139" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
@@ -21883,11 +21883,11 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>0.6698501017118754</v>
+        <v>0.6030022756249189</v>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
@@ -21921,12 +21921,12 @@
       <c r="AJ140" t="inlineStr"/>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
@@ -22037,11 +22037,11 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>0.6527060768673527</v>
+        <v>0.5892445384058143</v>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
@@ -22075,12 +22075,12 @@
       <c r="AJ141" t="inlineStr"/>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
@@ -22191,11 +22191,11 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>0.6447573951854262</v>
+        <v>0.5822573951854264</v>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
@@ -22229,12 +22229,12 @@
       <c r="AJ142" t="inlineStr"/>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -22345,11 +22345,11 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>0.6392777009051284</v>
+        <v>0.5772584701358976</v>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
@@ -22383,12 +22383,12 @@
       <c r="AJ143" t="inlineStr"/>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -22499,7 +22499,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>0.5972970809072762</v>
+        <v>0.5879220809072763</v>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
@@ -22537,12 +22537,12 @@
       <c r="AJ144" t="inlineStr"/>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL144" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM144" t="inlineStr">
@@ -22653,11 +22653,11 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>0.6166934899578748</v>
+        <v>0.5716934899578747</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
@@ -22691,12 +22691,12 @@
       <c r="AJ145" t="inlineStr"/>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -22845,12 +22845,12 @@
       <c r="AJ146" t="inlineStr"/>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
@@ -22999,12 +22999,12 @@
       <c r="AJ147" t="inlineStr"/>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -23115,11 +23115,11 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>0.6276684441463908</v>
+        <v>0.5750088696783058</v>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
@@ -23153,12 +23153,12 @@
       <c r="AJ148" t="inlineStr"/>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -23307,12 +23307,12 @@
       <c r="AJ149" t="inlineStr"/>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
@@ -23461,12 +23461,12 @@
       <c r="AJ150" t="inlineStr"/>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
@@ -23615,12 +23615,12 @@
       <c r="AJ151" t="inlineStr"/>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -23769,12 +23769,12 @@
       <c r="AJ152" t="inlineStr"/>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
@@ -23923,12 +23923,12 @@
       <c r="AJ153" t="inlineStr"/>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
@@ -24077,12 +24077,12 @@
       <c r="AJ154" t="inlineStr"/>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
@@ -24231,12 +24231,12 @@
       <c r="AJ155" t="inlineStr"/>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
@@ -24347,7 +24347,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>0.5929872027339661</v>
+        <v>0.592987202733966</v>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
@@ -24385,12 +24385,12 @@
       <c r="AJ156" t="inlineStr"/>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
@@ -24539,12 +24539,12 @@
       <c r="AJ157" t="inlineStr"/>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
@@ -24693,12 +24693,12 @@
       <c r="AJ158" t="inlineStr"/>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM158" t="inlineStr">
@@ -24809,7 +24809,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>0.6103194620235723</v>
+        <v>0.6103194620235722</v>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
@@ -24847,12 +24847,12 @@
       <c r="AJ159" t="inlineStr"/>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL159" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM159" t="inlineStr">
@@ -25001,12 +25001,12 @@
       <c r="AJ160" t="inlineStr"/>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
@@ -25117,7 +25117,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>0.6442084060577722</v>
+        <v>0.644208406057772</v>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
@@ -25155,12 +25155,12 @@
       <c r="AJ161" t="inlineStr"/>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
@@ -25271,7 +25271,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>0.5991609836554675</v>
+        <v>0.5991609836554674</v>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
@@ -25309,12 +25309,12 @@
       <c r="AJ162" t="inlineStr"/>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
@@ -25463,12 +25463,12 @@
       <c r="AJ163" t="inlineStr"/>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM163" t="inlineStr">
@@ -25617,12 +25617,12 @@
       <c r="AJ164" t="inlineStr"/>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL164" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM164" t="inlineStr">
@@ -25733,7 +25733,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>0.5450670932566559</v>
+        <v>0.5450670932566557</v>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
@@ -25771,12 +25771,12 @@
       <c r="AJ165" t="inlineStr"/>
       <c r="AK165" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL165" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM165" t="inlineStr">
@@ -25921,12 +25921,12 @@
       <c r="AJ166" t="inlineStr"/>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM166" t="inlineStr">
@@ -26075,12 +26075,12 @@
       <c r="AJ167" t="inlineStr"/>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
@@ -26191,7 +26191,7 @@
         </is>
       </c>
       <c r="Z168" t="n">
-        <v>0.5571795069868158</v>
+        <v>0.5571795069868157</v>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
@@ -26229,12 +26229,12 @@
       <c r="AJ168" t="inlineStr"/>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL168" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM168" t="inlineStr">
@@ -26379,12 +26379,12 @@
       <c r="AJ169" t="inlineStr"/>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL169" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
@@ -26529,12 +26529,12 @@
       <c r="AJ170" t="inlineStr"/>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL170" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM170" t="inlineStr">
@@ -26641,7 +26641,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>0.579419829530708</v>
+        <v>0.5794198295307079</v>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
@@ -26679,12 +26679,12 @@
       <c r="AJ171" t="inlineStr"/>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL171" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM171" t="inlineStr">
@@ -26829,12 +26829,12 @@
       <c r="AJ172" t="inlineStr"/>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
@@ -26979,12 +26979,12 @@
       <c r="AJ173" t="inlineStr"/>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -27129,12 +27129,12 @@
       <c r="AJ174" t="inlineStr"/>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
@@ -27279,12 +27279,12 @@
       <c r="AJ175" t="inlineStr"/>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
@@ -27391,7 +27391,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>0.6198853873452131</v>
+        <v>0.6198853873452133</v>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
@@ -27429,12 +27429,12 @@
       <c r="AJ176" t="inlineStr"/>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL176" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM176" t="inlineStr">
@@ -27579,12 +27579,12 @@
       <c r="AJ177" t="inlineStr"/>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
@@ -27729,12 +27729,12 @@
       <c r="AJ178" t="inlineStr"/>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL178" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM178" t="inlineStr">
@@ -27879,12 +27879,12 @@
       <c r="AJ179" t="inlineStr"/>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL179" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM179" t="inlineStr">
@@ -28029,12 +28029,12 @@
       <c r="AJ180" t="inlineStr"/>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM180" t="inlineStr">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>0.633904335171568</v>
+        <v>0.6339043351715679</v>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
@@ -28179,12 +28179,12 @@
       <c r="AJ181" t="inlineStr"/>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
@@ -28329,12 +28329,12 @@
       <c r="AJ182" t="inlineStr"/>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
@@ -28441,7 +28441,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>0.6259883763559191</v>
+        <v>0.625988376355919</v>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
@@ -28479,12 +28479,12 @@
       <c r="AJ183" t="inlineStr"/>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL183" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM183" t="inlineStr">
@@ -28629,12 +28629,12 @@
       <c r="AJ184" t="inlineStr"/>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL184" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM184" t="inlineStr">
@@ -28779,12 +28779,12 @@
       <c r="AJ185" t="inlineStr"/>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL185" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM185" t="inlineStr">
@@ -28929,12 +28929,12 @@
       <c r="AJ186" t="inlineStr"/>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL186" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM186" t="inlineStr">
@@ -29041,7 +29041,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>0.6058022414675892</v>
+        <v>0.6058022414675891</v>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
@@ -29079,12 +29079,12 @@
       <c r="AJ187" t="inlineStr"/>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
@@ -29191,7 +29191,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>0.628844906528938</v>
+        <v>0.6288449065289379</v>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
@@ -29229,12 +29229,12 @@
       <c r="AJ188" t="inlineStr"/>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL188" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM188" t="inlineStr">
@@ -29345,11 +29345,11 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>0.6951247267236547</v>
+        <v>0.6201247267236548</v>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr">
@@ -29383,12 +29383,12 @@
       <c r="AJ189" t="inlineStr"/>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL189" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
@@ -29499,11 +29499,11 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>0.6945032917596854</v>
+        <v>0.6195032917596855</v>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr">
@@ -29537,12 +29537,12 @@
       <c r="AJ190" t="inlineStr"/>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL190" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM190" t="inlineStr">
@@ -29653,11 +29653,11 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>0.7111305543718611</v>
+        <v>0.6361305543718612</v>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
@@ -29691,12 +29691,12 @@
       <c r="AJ191" t="inlineStr"/>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL191" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
@@ -29807,11 +29807,11 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>0.6537006347951428</v>
+        <v>0.601777557872066</v>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
@@ -29845,12 +29845,12 @@
       <c r="AJ192" t="inlineStr"/>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
@@ -29961,11 +29961,11 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>0.6239726400994291</v>
+        <v>0.5824953673721561</v>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
@@ -29999,12 +29999,12 @@
       <c r="AJ193" t="inlineStr"/>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
@@ -30115,11 +30115,11 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>0.6612646348273155</v>
+        <v>0.5976485633987441</v>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
@@ -30153,12 +30153,12 @@
       <c r="AJ194" t="inlineStr"/>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL194" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM194" t="inlineStr">
@@ -30307,12 +30307,12 @@
       <c r="AJ195" t="inlineStr"/>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL195" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM195" t="inlineStr">
@@ -30461,12 +30461,12 @@
       <c r="AJ196" t="inlineStr"/>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL196" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM196" t="inlineStr">
@@ -30577,7 +30577,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>0.5943318336168536</v>
+        <v>0.5791532621882821</v>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
@@ -30615,12 +30615,12 @@
       <c r="AJ197" t="inlineStr"/>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL197" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
@@ -30769,12 +30769,12 @@
       <c r="AJ198" t="inlineStr"/>
       <c r="AK198" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL198" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM198" t="inlineStr">
@@ -30885,7 +30885,7 @@
         </is>
       </c>
       <c r="Z199" t="n">
-        <v>0.6329676834748165</v>
+        <v>0.6329676834748162</v>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
@@ -30923,12 +30923,12 @@
       <c r="AJ199" t="inlineStr"/>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
@@ -31077,12 +31077,12 @@
       <c r="AJ200" t="inlineStr"/>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
@@ -31231,12 +31231,12 @@
       <c r="AJ201" t="inlineStr"/>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL201" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
@@ -31385,12 +31385,12 @@
       <c r="AJ202" t="inlineStr"/>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL202" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM202" t="inlineStr">
@@ -31539,12 +31539,12 @@
       <c r="AJ203" t="inlineStr"/>
       <c r="AK203" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL203" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM203" t="inlineStr">
@@ -31693,12 +31693,12 @@
       <c r="AJ204" t="inlineStr"/>
       <c r="AK204" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL204" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM204" t="inlineStr">
@@ -31847,12 +31847,12 @@
       <c r="AJ205" t="inlineStr"/>
       <c r="AK205" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL205" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM205" t="inlineStr">
@@ -32001,12 +32001,12 @@
       <c r="AJ206" t="inlineStr"/>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL206" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM206" t="inlineStr">
@@ -32155,12 +32155,12 @@
       <c r="AJ207" t="inlineStr"/>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
@@ -32309,12 +32309,12 @@
       <c r="AJ208" t="inlineStr"/>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
@@ -32463,12 +32463,12 @@
       <c r="AJ209" t="inlineStr"/>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
@@ -32579,7 +32579,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>0.5650646664660511</v>
+        <v>0.565064666466051</v>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
@@ -32617,12 +32617,12 @@
       <c r="AJ210" t="inlineStr"/>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL210" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM210" t="inlineStr">
@@ -32729,7 +32729,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>0.6259182065264314</v>
+        <v>0.6259182065264315</v>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
@@ -32767,12 +32767,12 @@
       <c r="AJ211" t="inlineStr"/>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL211" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM211" t="inlineStr">
@@ -32917,12 +32917,12 @@
       <c r="AJ212" t="inlineStr"/>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL212" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
@@ -33067,12 +33067,12 @@
       <c r="AJ213" t="inlineStr"/>
       <c r="AK213" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL213" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM213" t="inlineStr">
@@ -33217,12 +33217,12 @@
       <c r="AJ214" t="inlineStr"/>
       <c r="AK214" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL214" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM214" t="inlineStr">
@@ -33367,12 +33367,12 @@
       <c r="AJ215" t="inlineStr"/>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL215" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM215" t="inlineStr">
@@ -33517,12 +33517,12 @@
       <c r="AJ216" t="inlineStr"/>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM216" t="inlineStr">
@@ -33629,7 +33629,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>0.5949188642841573</v>
+        <v>0.5949188642841572</v>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
@@ -33667,12 +33667,12 @@
       <c r="AJ217" t="inlineStr"/>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
@@ -33817,12 +33817,12 @@
       <c r="AJ218" t="inlineStr"/>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM218" t="inlineStr">
@@ -33967,12 +33967,12 @@
       <c r="AJ219" t="inlineStr"/>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM219" t="inlineStr">
@@ -34117,12 +34117,12 @@
       <c r="AJ220" t="inlineStr"/>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
@@ -34229,7 +34229,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>0.6219039380922436</v>
+        <v>0.6219039380922434</v>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
@@ -34267,12 +34267,12 @@
       <c r="AJ221" t="inlineStr"/>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL221" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM221" t="inlineStr">
@@ -34417,12 +34417,12 @@
       <c r="AJ222" t="inlineStr"/>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
@@ -34567,12 +34567,12 @@
       <c r="AJ223" t="inlineStr"/>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
@@ -34717,12 +34717,12 @@
       <c r="AJ224" t="inlineStr"/>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
@@ -34871,12 +34871,12 @@
       <c r="AJ225" t="inlineStr"/>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM225" t="inlineStr">
@@ -35025,12 +35025,12 @@
       <c r="AJ226" t="inlineStr"/>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -35179,12 +35179,12 @@
       <c r="AJ227" t="inlineStr"/>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
@@ -35333,12 +35333,12 @@
       <c r="AJ228" t="inlineStr"/>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
@@ -35449,7 +35449,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>0.7040929177092436</v>
+        <v>0.7040929177092435</v>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
@@ -35487,12 +35487,12 @@
       <c r="AJ229" t="inlineStr"/>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
@@ -35641,12 +35641,12 @@
       <c r="AJ230" t="inlineStr"/>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
@@ -35795,12 +35795,12 @@
       <c r="AJ231" t="inlineStr"/>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
@@ -35949,12 +35949,12 @@
       <c r="AJ232" t="inlineStr"/>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM232" t="inlineStr">
@@ -36103,12 +36103,12 @@
       <c r="AJ233" t="inlineStr"/>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
@@ -36257,12 +36257,12 @@
       <c r="AJ234" t="inlineStr"/>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
@@ -36411,12 +36411,12 @@
       <c r="AJ235" t="inlineStr"/>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
@@ -36565,12 +36565,12 @@
       <c r="AJ236" t="inlineStr"/>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
@@ -36719,12 +36719,12 @@
       <c r="AJ237" t="inlineStr"/>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
@@ -36873,12 +36873,12 @@
       <c r="AJ238" t="inlineStr"/>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -37027,12 +37027,12 @@
       <c r="AJ239" t="inlineStr"/>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL239" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM239" t="inlineStr">
@@ -37143,7 +37143,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>0.5981323417986512</v>
+        <v>0.598132341798651</v>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
@@ -37181,12 +37181,12 @@
       <c r="AJ240" t="inlineStr"/>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL240" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM240" t="inlineStr">
@@ -37335,12 +37335,12 @@
       <c r="AJ241" t="inlineStr"/>
       <c r="AK241" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL241" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM241" t="inlineStr">
@@ -37489,12 +37489,12 @@
       <c r="AJ242" t="inlineStr"/>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL242" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM242" t="inlineStr">
@@ -37643,12 +37643,12 @@
       <c r="AJ243" t="inlineStr"/>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL243" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM243" t="inlineStr">
@@ -37759,7 +37759,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>0.5792120449258175</v>
+        <v>0.5792120449258173</v>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
@@ -37797,12 +37797,12 @@
       <c r="AJ244" t="inlineStr"/>
       <c r="AK244" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL244" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM244" t="inlineStr">
@@ -37951,12 +37951,12 @@
       <c r="AJ245" t="inlineStr"/>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL245" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM245" t="inlineStr">
@@ -38105,12 +38105,12 @@
       <c r="AJ246" t="inlineStr"/>
       <c r="AK246" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL246" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM246" t="inlineStr">
@@ -38259,12 +38259,12 @@
       <c r="AJ247" t="inlineStr"/>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL247" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
@@ -38413,12 +38413,12 @@
       <c r="AJ248" t="inlineStr"/>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL248" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM248" t="inlineStr">
@@ -38567,12 +38567,12 @@
       <c r="AJ249" t="inlineStr"/>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL249" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
@@ -38717,12 +38717,12 @@
       <c r="AJ250" t="inlineStr"/>
       <c r="AK250" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL250" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM250" t="inlineStr">
@@ -38871,12 +38871,12 @@
       <c r="AJ251" t="inlineStr"/>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL251" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
@@ -39021,12 +39021,12 @@
       <c r="AJ252" t="inlineStr"/>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL252" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM252" t="inlineStr">
@@ -39171,12 +39171,12 @@
       <c r="AJ253" t="inlineStr"/>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL253" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
@@ -39321,12 +39321,12 @@
       <c r="AJ254" t="inlineStr"/>
       <c r="AK254" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL254" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM254" t="inlineStr">
@@ -39471,12 +39471,12 @@
       <c r="AJ255" t="inlineStr"/>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL255" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM255" t="inlineStr">
@@ -39583,7 +39583,7 @@
         </is>
       </c>
       <c r="Z256" t="n">
-        <v>0.6325785251888171</v>
+        <v>0.6325785251888172</v>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
@@ -39621,12 +39621,12 @@
       <c r="AJ256" t="inlineStr"/>
       <c r="AK256" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL256" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM256" t="inlineStr">
@@ -39771,12 +39771,12 @@
       <c r="AJ257" t="inlineStr"/>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL257" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM257" t="inlineStr">
@@ -39921,12 +39921,12 @@
       <c r="AJ258" t="inlineStr"/>
       <c r="AK258" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL258" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM258" t="inlineStr">
@@ -40071,12 +40071,12 @@
       <c r="AJ259" t="inlineStr"/>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL259" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM259" t="inlineStr">
@@ -40221,12 +40221,12 @@
       <c r="AJ260" t="inlineStr"/>
       <c r="AK260" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL260" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM260" t="inlineStr">
@@ -40333,7 +40333,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>0.5836632379747914</v>
+        <v>0.5836632379747912</v>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
@@ -40371,12 +40371,12 @@
       <c r="AJ261" t="inlineStr"/>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL261" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM261" t="inlineStr">
@@ -40521,12 +40521,12 @@
       <c r="AJ262" t="inlineStr"/>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL262" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM262" t="inlineStr">
@@ -40637,11 +40637,11 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>0.7190610740007666</v>
+        <v>0.6440610740007666</v>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB263" t="inlineStr">
@@ -40675,12 +40675,12 @@
       <c r="AJ263" t="inlineStr"/>
       <c r="AK263" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL263" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM263" t="inlineStr">
@@ -40791,11 +40791,11 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>0.7008514482680345</v>
+        <v>0.6258514482680346</v>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB264" t="inlineStr">
@@ -40829,12 +40829,12 @@
       <c r="AJ264" t="inlineStr"/>
       <c r="AK264" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL264" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM264" t="inlineStr">
@@ -40945,11 +40945,11 @@
         </is>
       </c>
       <c r="Z265" t="n">
-        <v>0.6537006347951428</v>
+        <v>0.601777557872066</v>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr">
@@ -40983,12 +40983,12 @@
       <c r="AJ265" t="inlineStr"/>
       <c r="AK265" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL265" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM265" t="inlineStr">
@@ -41099,11 +41099,11 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>0.7175826143005893</v>
+        <v>0.6425826143005894</v>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
@@ -41137,12 +41137,12 @@
       <c r="AJ266" t="inlineStr"/>
       <c r="AK266" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL266" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM266" t="inlineStr">
@@ -41253,11 +41253,11 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>0.6359866474468285</v>
+        <v>0.5836945365726282</v>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB267" t="inlineStr">
@@ -41291,12 +41291,12 @@
       <c r="AJ267" t="inlineStr"/>
       <c r="AK267" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL267" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM267" t="inlineStr">
@@ -41407,11 +41407,11 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>0.6276475334575058</v>
+        <v>0.5742893245022821</v>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB268" t="inlineStr">
@@ -41445,12 +41445,12 @@
       <c r="AJ268" t="inlineStr"/>
       <c r="AK268" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL268" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM268" t="inlineStr">
@@ -41599,12 +41599,12 @@
       <c r="AJ269" t="inlineStr"/>
       <c r="AK269" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL269" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM269" t="inlineStr">
@@ -41753,12 +41753,12 @@
       <c r="AJ270" t="inlineStr"/>
       <c r="AK270" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL270" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM270" t="inlineStr">
@@ -41907,12 +41907,12 @@
       <c r="AJ271" t="inlineStr"/>
       <c r="AK271" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL271" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM271" t="inlineStr">
@@ -42061,12 +42061,12 @@
       <c r="AJ272" t="inlineStr"/>
       <c r="AK272" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL272" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM272" t="inlineStr">
@@ -42215,12 +42215,12 @@
       <c r="AJ273" t="inlineStr"/>
       <c r="AK273" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL273" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM273" t="inlineStr">
@@ -42331,7 +42331,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>0.5199574702462262</v>
+        <v>0.5199574702462261</v>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
@@ -42369,12 +42369,12 @@
       <c r="AJ274" t="inlineStr"/>
       <c r="AK274" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL274" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM274" t="inlineStr">
@@ -42485,7 +42485,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>0.5983834619496874</v>
+        <v>0.5983834619496873</v>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
@@ -42523,12 +42523,12 @@
       <c r="AJ275" t="inlineStr"/>
       <c r="AK275" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL275" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM275" t="inlineStr">
@@ -42677,12 +42677,12 @@
       <c r="AJ276" t="inlineStr"/>
       <c r="AK276" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL276" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM276" t="inlineStr">
@@ -42831,12 +42831,12 @@
       <c r="AJ277" t="inlineStr"/>
       <c r="AK277" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL277" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM277" t="inlineStr">
@@ -42985,12 +42985,12 @@
       <c r="AJ278" t="inlineStr"/>
       <c r="AK278" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL278" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM278" t="inlineStr">
@@ -43101,7 +43101,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>0.5576087664351743</v>
+        <v>0.5576087664351742</v>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
@@ -43139,12 +43139,12 @@
       <c r="AJ279" t="inlineStr"/>
       <c r="AK279" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL279" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM279" t="inlineStr">
@@ -43251,7 +43251,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>0.52852197326353</v>
+        <v>0.5285219732635301</v>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
@@ -43289,12 +43289,12 @@
       <c r="AJ280" t="inlineStr"/>
       <c r="AK280" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL280" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM280" t="inlineStr">
@@ -43439,12 +43439,12 @@
       <c r="AJ281" t="inlineStr"/>
       <c r="AK281" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL281" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM281" t="inlineStr">
@@ -43593,12 +43593,12 @@
       <c r="AJ282" t="inlineStr"/>
       <c r="AK282" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL282" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM282" t="inlineStr">
@@ -43743,12 +43743,12 @@
       <c r="AJ283" t="inlineStr"/>
       <c r="AK283" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL283" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM283" t="inlineStr">
@@ -43855,7 +43855,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>0.6208424600203839</v>
+        <v>0.620842460020384</v>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
@@ -43893,12 +43893,12 @@
       <c r="AJ284" t="inlineStr"/>
       <c r="AK284" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL284" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM284" t="inlineStr">
@@ -44043,12 +44043,12 @@
       <c r="AJ285" t="inlineStr"/>
       <c r="AK285" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL285" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM285" t="inlineStr">
@@ -44193,12 +44193,12 @@
       <c r="AJ286" t="inlineStr"/>
       <c r="AK286" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL286" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM286" t="inlineStr">
@@ -44343,12 +44343,12 @@
       <c r="AJ287" t="inlineStr"/>
       <c r="AK287" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL287" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM287" t="inlineStr">
@@ -44493,12 +44493,12 @@
       <c r="AJ288" t="inlineStr"/>
       <c r="AK288" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL288" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM288" t="inlineStr">
@@ -44643,12 +44643,12 @@
       <c r="AJ289" t="inlineStr"/>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL289" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM289" t="inlineStr">
@@ -44755,7 +44755,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>0.6246510596601756</v>
+        <v>0.6246510596601755</v>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
@@ -44793,12 +44793,12 @@
       <c r="AJ290" t="inlineStr"/>
       <c r="AK290" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL290" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM290" t="inlineStr">
@@ -44905,7 +44905,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>0.615553549567695</v>
+        <v>0.6155535495676949</v>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
@@ -44943,12 +44943,12 @@
       <c r="AJ291" t="inlineStr"/>
       <c r="AK291" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL291" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM291" t="inlineStr">
@@ -45093,12 +45093,12 @@
       <c r="AJ292" t="inlineStr"/>
       <c r="AK292" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL292" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM292" t="inlineStr">
@@ -45243,12 +45243,12 @@
       <c r="AJ293" t="inlineStr"/>
       <c r="AK293" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL293" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM293" t="inlineStr">
@@ -45393,12 +45393,12 @@
       <c r="AJ294" t="inlineStr"/>
       <c r="AK294" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL294" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM294" t="inlineStr">
@@ -45543,12 +45543,12 @@
       <c r="AJ295" t="inlineStr"/>
       <c r="AK295" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL295" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM295" t="inlineStr">
@@ -45693,12 +45693,12 @@
       <c r="AJ296" t="inlineStr"/>
       <c r="AK296" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL296" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM296" t="inlineStr">
@@ -45805,7 +45805,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>0.6107468271852798</v>
+        <v>0.6107468271852797</v>
       </c>
       <c r="AA297" t="inlineStr">
         <is>
@@ -45843,12 +45843,12 @@
       <c r="AJ297" t="inlineStr"/>
       <c r="AK297" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL297" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM297" t="inlineStr">
@@ -45993,12 +45993,12 @@
       <c r="AJ298" t="inlineStr"/>
       <c r="AK298" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL298" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM298" t="inlineStr">
@@ -46143,12 +46143,12 @@
       <c r="AJ299" t="inlineStr"/>
       <c r="AK299" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL299" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM299" t="inlineStr">
@@ -46259,11 +46259,11 @@
         </is>
       </c>
       <c r="Z300" t="n">
-        <v>0.7478423811730142</v>
+        <v>0.6728423811730142</v>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB300" t="inlineStr">
@@ -46297,12 +46297,12 @@
       <c r="AJ300" t="inlineStr"/>
       <c r="AK300" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL300" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM300" t="inlineStr">
@@ -46413,11 +46413,11 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>0.7384775855922865</v>
+        <v>0.6634775855922863</v>
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB301" t="inlineStr">
@@ -46451,12 +46451,12 @@
       <c r="AJ301" t="inlineStr"/>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL301" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM301" t="inlineStr">
@@ -46567,11 +46567,11 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>0.7008655725618199</v>
+        <v>0.62586557256182</v>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB302" t="inlineStr">
@@ -46605,12 +46605,12 @@
       <c r="AJ302" t="inlineStr"/>
       <c r="AK302" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL302" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM302" t="inlineStr">
@@ -46721,11 +46721,11 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>0.6537006347951428</v>
+        <v>0.601777557872066</v>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB303" t="inlineStr">
@@ -46759,12 +46759,12 @@
       <c r="AJ303" t="inlineStr"/>
       <c r="AK303" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL303" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM303" t="inlineStr">
@@ -46875,11 +46875,11 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>0.6313187062416483</v>
+        <v>0.5848463136036114</v>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB304" t="inlineStr">
@@ -46913,12 +46913,12 @@
       <c r="AJ304" t="inlineStr"/>
       <c r="AK304" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL304" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM304" t="inlineStr">
@@ -47029,11 +47029,11 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>0.6669126656150276</v>
+        <v>0.6030613142636763</v>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB305" t="inlineStr">
@@ -47067,12 +47067,12 @@
       <c r="AJ305" t="inlineStr"/>
       <c r="AK305" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL305" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM305" t="inlineStr">
@@ -47221,12 +47221,12 @@
       <c r="AJ306" t="inlineStr"/>
       <c r="AK306" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL306" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM306" t="inlineStr">
@@ -47375,12 +47375,12 @@
       <c r="AJ307" t="inlineStr"/>
       <c r="AK307" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL307" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM307" t="inlineStr">
@@ -47491,7 +47491,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>0.6064924588820425</v>
+        <v>0.5777541411250331</v>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
@@ -47529,12 +47529,12 @@
       <c r="AJ308" t="inlineStr"/>
       <c r="AK308" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL308" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM308" t="inlineStr">
@@ -47645,11 +47645,11 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>0.6338793545904775</v>
+        <v>0.5733203483792974</v>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="AB309" t="inlineStr">
@@ -47683,12 +47683,12 @@
       <c r="AJ309" t="inlineStr"/>
       <c r="AK309" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL309" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM309" t="inlineStr">
@@ -47837,12 +47837,12 @@
       <c r="AJ310" t="inlineStr"/>
       <c r="AK310" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL310" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM310" t="inlineStr">
@@ -47991,12 +47991,12 @@
       <c r="AJ311" t="inlineStr"/>
       <c r="AK311" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL311" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM311" t="inlineStr">
@@ -48145,12 +48145,12 @@
       <c r="AJ312" t="inlineStr"/>
       <c r="AK312" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL312" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM312" t="inlineStr">
@@ -48299,12 +48299,12 @@
       <c r="AJ313" t="inlineStr"/>
       <c r="AK313" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL313" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM313" t="inlineStr">
@@ -48453,12 +48453,12 @@
       <c r="AJ314" t="inlineStr"/>
       <c r="AK314" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL314" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM314" t="inlineStr">
@@ -48569,7 +48569,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>0.6151180449969718</v>
+        <v>0.6151180449969716</v>
       </c>
       <c r="AA315" t="inlineStr">
         <is>
@@ -48607,12 +48607,12 @@
       <c r="AJ315" t="inlineStr"/>
       <c r="AK315" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL315" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM315" t="inlineStr">
@@ -48761,12 +48761,12 @@
       <c r="AJ316" t="inlineStr"/>
       <c r="AK316" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL316" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM316" t="inlineStr">
@@ -48915,12 +48915,12 @@
       <c r="AJ317" t="inlineStr"/>
       <c r="AK317" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL317" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM317" t="inlineStr">
@@ -49069,12 +49069,12 @@
       <c r="AJ318" t="inlineStr"/>
       <c r="AK318" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL318" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM318" t="inlineStr">
@@ -49223,12 +49223,12 @@
       <c r="AJ319" t="inlineStr"/>
       <c r="AK319" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL319" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM319" t="inlineStr">
@@ -49377,12 +49377,12 @@
       <c r="AJ320" t="inlineStr"/>
       <c r="AK320" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL320" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM320" t="inlineStr">
@@ -49531,12 +49531,12 @@
       <c r="AJ321" t="inlineStr"/>
       <c r="AK321" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL321" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM321" t="inlineStr">
@@ -49685,12 +49685,12 @@
       <c r="AJ322" t="inlineStr"/>
       <c r="AK322" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL322" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM322" t="inlineStr">
@@ -49801,7 +49801,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>0.5802782690417198</v>
+        <v>0.5802782690417196</v>
       </c>
       <c r="AA323" t="inlineStr">
         <is>
@@ -49839,12 +49839,12 @@
       <c r="AJ323" t="inlineStr"/>
       <c r="AK323" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL323" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM323" t="inlineStr">
@@ -49993,12 +49993,12 @@
       <c r="AJ324" t="inlineStr"/>
       <c r="AK324" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL324" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM324" t="inlineStr">
@@ -50147,12 +50147,12 @@
       <c r="AJ325" t="inlineStr"/>
       <c r="AK325" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL325" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM325" t="inlineStr">
@@ -50301,12 +50301,12 @@
       <c r="AJ326" t="inlineStr"/>
       <c r="AK326" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL326" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM326" t="inlineStr">
@@ -50451,12 +50451,12 @@
       <c r="AJ327" t="inlineStr"/>
       <c r="AK327" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL327" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM327" t="inlineStr">
@@ -50601,12 +50601,12 @@
       <c r="AJ328" t="inlineStr"/>
       <c r="AK328" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL328" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM328" t="inlineStr">
@@ -50713,7 +50713,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>0.6162367897783875</v>
+        <v>0.6162367897783876</v>
       </c>
       <c r="AA329" t="inlineStr">
         <is>
@@ -50751,12 +50751,12 @@
       <c r="AJ329" t="inlineStr"/>
       <c r="AK329" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL329" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM329" t="inlineStr">
@@ -50901,12 +50901,12 @@
       <c r="AJ330" t="inlineStr"/>
       <c r="AK330" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL330" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM330" t="inlineStr">
@@ -51051,12 +51051,12 @@
       <c r="AJ331" t="inlineStr"/>
       <c r="AK331" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL331" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM331" t="inlineStr">
@@ -51201,12 +51201,12 @@
       <c r="AJ332" t="inlineStr"/>
       <c r="AK332" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL332" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM332" t="inlineStr">
@@ -51351,12 +51351,12 @@
       <c r="AJ333" t="inlineStr"/>
       <c r="AK333" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL333" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM333" t="inlineStr">
@@ -51501,12 +51501,12 @@
       <c r="AJ334" t="inlineStr"/>
       <c r="AK334" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL334" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM334" t="inlineStr">
@@ -51651,12 +51651,12 @@
       <c r="AJ335" t="inlineStr"/>
       <c r="AK335" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL335" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM335" t="inlineStr">
@@ -51801,12 +51801,12 @@
       <c r="AJ336" t="inlineStr"/>
       <c r="AK336" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL336" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM336" t="inlineStr">
@@ -51913,7 +51913,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>0.6231819180667871</v>
+        <v>0.623181918066787</v>
       </c>
       <c r="AA337" t="inlineStr">
         <is>
@@ -51951,12 +51951,12 @@
       <c r="AJ337" t="inlineStr"/>
       <c r="AK337" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL337" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM337" t="inlineStr">
@@ -52101,12 +52101,12 @@
       <c r="AJ338" t="inlineStr"/>
       <c r="AK338" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL338" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM338" t="inlineStr">
@@ -52213,7 +52213,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>0.6150088148320375</v>
+        <v>0.6150088148320374</v>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
@@ -52251,12 +52251,12 @@
       <c r="AJ339" t="inlineStr"/>
       <c r="AK339" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL339" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM339" t="inlineStr">
@@ -52401,12 +52401,12 @@
       <c r="AJ340" t="inlineStr"/>
       <c r="AK340" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL340" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM340" t="inlineStr">
@@ -52551,12 +52551,12 @@
       <c r="AJ341" t="inlineStr"/>
       <c r="AK341" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL341" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM341" t="inlineStr">
@@ -52701,12 +52701,12 @@
       <c r="AJ342" t="inlineStr"/>
       <c r="AK342" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL342" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM342" t="inlineStr">
@@ -52851,12 +52851,12 @@
       <c r="AJ343" t="inlineStr"/>
       <c r="AK343" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL343" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM343" t="inlineStr">
@@ -53001,12 +53001,12 @@
       <c r="AJ344" t="inlineStr"/>
       <c r="AK344" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL344" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM344" t="inlineStr">
@@ -53113,7 +53113,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>0.6054155334088336</v>
+        <v>0.6054155334088335</v>
       </c>
       <c r="AA345" t="inlineStr">
         <is>
@@ -53151,12 +53151,12 @@
       <c r="AJ345" t="inlineStr"/>
       <c r="AK345" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL345" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM345" t="inlineStr">
@@ -53301,12 +53301,12 @@
       <c r="AJ346" t="inlineStr"/>
       <c r="AK346" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL346" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM346" t="inlineStr">
@@ -53451,12 +53451,12 @@
       <c r="AJ347" t="inlineStr"/>
       <c r="AK347" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL347" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM347" t="inlineStr">
@@ -53601,12 +53601,12 @@
       <c r="AJ348" t="inlineStr"/>
       <c r="AK348" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL348" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM348" t="inlineStr">
@@ -53751,12 +53751,12 @@
       <c r="AJ349" t="inlineStr"/>
       <c r="AK349" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL349" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM349" t="inlineStr">
@@ -53905,12 +53905,12 @@
       <c r="AJ350" t="inlineStr"/>
       <c r="AK350" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL350" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM350" t="inlineStr">
@@ -54059,12 +54059,12 @@
       <c r="AJ351" t="inlineStr"/>
       <c r="AK351" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL351" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM351" t="inlineStr">
@@ -54175,7 +54175,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>0.7596745095657554</v>
+        <v>0.7596745095657557</v>
       </c>
       <c r="AA352" t="inlineStr">
         <is>
@@ -54213,12 +54213,12 @@
       <c r="AJ352" t="inlineStr"/>
       <c r="AK352" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL352" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM352" t="inlineStr">
@@ -54367,12 +54367,12 @@
       <c r="AJ353" t="inlineStr"/>
       <c r="AK353" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL353" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM353" t="inlineStr">
@@ -54521,12 +54521,12 @@
       <c r="AJ354" t="inlineStr"/>
       <c r="AK354" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL354" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM354" t="inlineStr">
@@ -54675,12 +54675,12 @@
       <c r="AJ355" t="inlineStr"/>
       <c r="AK355" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL355" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM355" t="inlineStr">
@@ -54829,12 +54829,12 @@
       <c r="AJ356" t="inlineStr"/>
       <c r="AK356" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL356" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM356" t="inlineStr">
@@ -54983,12 +54983,12 @@
       <c r="AJ357" t="inlineStr"/>
       <c r="AK357" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL357" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM357" t="inlineStr">
@@ -55137,12 +55137,12 @@
       <c r="AJ358" t="inlineStr"/>
       <c r="AK358" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL358" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM358" t="inlineStr">
@@ -55291,12 +55291,12 @@
       <c r="AJ359" t="inlineStr"/>
       <c r="AK359" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL359" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM359" t="inlineStr">
@@ -55445,12 +55445,12 @@
       <c r="AJ360" t="inlineStr"/>
       <c r="AK360" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL360" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM360" t="inlineStr">
@@ -55599,12 +55599,12 @@
       <c r="AJ361" t="inlineStr"/>
       <c r="AK361" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL361" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM361" t="inlineStr">
@@ -55715,7 +55715,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>0.5974562952367269</v>
+        <v>0.5974562952367267</v>
       </c>
       <c r="AA362" t="inlineStr">
         <is>
@@ -55753,12 +55753,12 @@
       <c r="AJ362" t="inlineStr"/>
       <c r="AK362" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL362" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM362" t="inlineStr">
@@ -55869,7 +55869,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>0.6499548587690245</v>
+        <v>0.6499548587690244</v>
       </c>
       <c r="AA363" t="inlineStr">
         <is>
@@ -55907,12 +55907,12 @@
       <c r="AJ363" t="inlineStr"/>
       <c r="AK363" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL363" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM363" t="inlineStr">
@@ -56061,12 +56061,12 @@
       <c r="AJ364" t="inlineStr"/>
       <c r="AK364" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL364" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM364" t="inlineStr">
@@ -56215,12 +56215,12 @@
       <c r="AJ365" t="inlineStr"/>
       <c r="AK365" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL365" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM365" t="inlineStr">
@@ -56369,12 +56369,12 @@
       <c r="AJ366" t="inlineStr"/>
       <c r="AK366" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL366" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM366" t="inlineStr">
@@ -56523,12 +56523,12 @@
       <c r="AJ367" t="inlineStr"/>
       <c r="AK367" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL367" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM367" t="inlineStr">
@@ -56677,12 +56677,12 @@
       <c r="AJ368" t="inlineStr"/>
       <c r="AK368" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL368" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM368" t="inlineStr">
@@ -56827,12 +56827,12 @@
       <c r="AJ369" t="inlineStr"/>
       <c r="AK369" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL369" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM369" t="inlineStr">
@@ -56977,12 +56977,12 @@
       <c r="AJ370" t="inlineStr"/>
       <c r="AK370" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL370" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM370" t="inlineStr">
@@ -57127,12 +57127,12 @@
       <c r="AJ371" t="inlineStr"/>
       <c r="AK371" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL371" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM371" t="inlineStr">
@@ -57277,12 +57277,12 @@
       <c r="AJ372" t="inlineStr"/>
       <c r="AK372" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL372" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM372" t="inlineStr">
@@ -57427,12 +57427,12 @@
       <c r="AJ373" t="inlineStr"/>
       <c r="AK373" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL373" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM373" t="inlineStr">
@@ -57539,7 +57539,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>0.7076185317097684</v>
+        <v>0.7076185317097683</v>
       </c>
       <c r="AA374" t="inlineStr">
         <is>
@@ -57577,12 +57577,12 @@
       <c r="AJ374" t="inlineStr"/>
       <c r="AK374" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL374" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM374" t="inlineStr">
@@ -57693,7 +57693,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>0.7615468907022023</v>
+        <v>0.7615468907022024</v>
       </c>
       <c r="AA375" t="inlineStr">
         <is>
@@ -57731,12 +57731,12 @@
       <c r="AJ375" t="inlineStr"/>
       <c r="AK375" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL375" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM375" t="inlineStr">
@@ -57885,12 +57885,12 @@
       <c r="AJ376" t="inlineStr"/>
       <c r="AK376" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL376" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM376" t="inlineStr">
@@ -58039,12 +58039,12 @@
       <c r="AJ377" t="inlineStr"/>
       <c r="AK377" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL377" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM377" t="inlineStr">
@@ -58193,12 +58193,12 @@
       <c r="AJ378" t="inlineStr"/>
       <c r="AK378" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL378" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM378" t="inlineStr">
@@ -58347,12 +58347,12 @@
       <c r="AJ379" t="inlineStr"/>
       <c r="AK379" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL379" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM379" t="inlineStr">
@@ -58501,12 +58501,12 @@
       <c r="AJ380" t="inlineStr"/>
       <c r="AK380" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL380" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM380" t="inlineStr">
@@ -58655,12 +58655,12 @@
       <c r="AJ381" t="inlineStr"/>
       <c r="AK381" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL381" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM381" t="inlineStr">
@@ -58809,12 +58809,12 @@
       <c r="AJ382" t="inlineStr"/>
       <c r="AK382" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL382" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM382" t="inlineStr">
@@ -58963,12 +58963,12 @@
       <c r="AJ383" t="inlineStr"/>
       <c r="AK383" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL383" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM383" t="inlineStr">
@@ -59117,12 +59117,12 @@
       <c r="AJ384" t="inlineStr"/>
       <c r="AK384" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL384" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM384" t="inlineStr">
@@ -59271,12 +59271,12 @@
       <c r="AJ385" t="inlineStr"/>
       <c r="AK385" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL385" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM385" t="inlineStr">
@@ -59421,12 +59421,12 @@
       <c r="AJ386" t="inlineStr"/>
       <c r="AK386" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL386" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM386" t="inlineStr">
@@ -59575,12 +59575,12 @@
       <c r="AJ387" t="inlineStr"/>
       <c r="AK387" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL387" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM387" t="inlineStr">
@@ -59729,12 +59729,12 @@
       <c r="AJ388" t="inlineStr"/>
       <c r="AK388" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL388" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM388" t="inlineStr">
@@ -59883,12 +59883,12 @@
       <c r="AJ389" t="inlineStr"/>
       <c r="AK389" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL389" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM389" t="inlineStr">
@@ -60037,12 +60037,12 @@
       <c r="AJ390" t="inlineStr"/>
       <c r="AK390" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL390" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM390" t="inlineStr">
@@ -60191,12 +60191,12 @@
       <c r="AJ391" t="inlineStr"/>
       <c r="AK391" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL391" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM391" t="inlineStr">
@@ -60307,7 +60307,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>0.6152104963021554</v>
+        <v>0.6152104963021553</v>
       </c>
       <c r="AA392" t="inlineStr">
         <is>
@@ -60345,12 +60345,12 @@
       <c r="AJ392" t="inlineStr"/>
       <c r="AK392" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL392" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM392" t="inlineStr">
@@ -60495,12 +60495,12 @@
       <c r="AJ393" t="inlineStr"/>
       <c r="AK393" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL393" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM393" t="inlineStr">
@@ -60645,12 +60645,12 @@
       <c r="AJ394" t="inlineStr"/>
       <c r="AK394" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL394" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM394" t="inlineStr">
@@ -60795,12 +60795,12 @@
       <c r="AJ395" t="inlineStr"/>
       <c r="AK395" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL395" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM395" t="inlineStr">
@@ -60945,12 +60945,12 @@
       <c r="AJ396" t="inlineStr"/>
       <c r="AK396" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL396" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM396" t="inlineStr">
@@ -61095,12 +61095,12 @@
       <c r="AJ397" t="inlineStr"/>
       <c r="AK397" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL397" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM397" t="inlineStr">
@@ -61245,12 +61245,12 @@
       <c r="AJ398" t="inlineStr"/>
       <c r="AK398" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL398" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM398" t="inlineStr">
@@ -61399,12 +61399,12 @@
       <c r="AJ399" t="inlineStr"/>
       <c r="AK399" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL399" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM399" t="inlineStr">
@@ -61553,12 +61553,12 @@
       <c r="AJ400" t="inlineStr"/>
       <c r="AK400" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL400" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM400" t="inlineStr">
@@ -61707,12 +61707,12 @@
       <c r="AJ401" t="inlineStr"/>
       <c r="AK401" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL401" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM401" t="inlineStr">
@@ -61861,12 +61861,12 @@
       <c r="AJ402" t="inlineStr"/>
       <c r="AK402" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL402" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM402" t="inlineStr">
@@ -62015,12 +62015,12 @@
       <c r="AJ403" t="inlineStr"/>
       <c r="AK403" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL403" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM403" t="inlineStr">
@@ -62169,12 +62169,12 @@
       <c r="AJ404" t="inlineStr"/>
       <c r="AK404" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL404" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM404" t="inlineStr">
@@ -62323,12 +62323,12 @@
       <c r="AJ405" t="inlineStr"/>
       <c r="AK405" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL405" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM405" t="inlineStr">
@@ -62477,12 +62477,12 @@
       <c r="AJ406" t="inlineStr"/>
       <c r="AK406" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL406" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM406" t="inlineStr">
@@ -62631,12 +62631,12 @@
       <c r="AJ407" t="inlineStr"/>
       <c r="AK407" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL407" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM407" t="inlineStr">
@@ -62785,12 +62785,12 @@
       <c r="AJ408" t="inlineStr"/>
       <c r="AK408" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL408" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM408" t="inlineStr">
@@ -62901,7 +62901,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>0.7798477245305743</v>
+        <v>0.7798477245305742</v>
       </c>
       <c r="AA409" t="inlineStr">
         <is>
@@ -62939,12 +62939,12 @@
       <c r="AJ409" t="inlineStr"/>
       <c r="AK409" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL409" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM409" t="inlineStr">
@@ -63093,12 +63093,12 @@
       <c r="AJ410" t="inlineStr"/>
       <c r="AK410" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL410" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM410" t="inlineStr">
@@ -63209,7 +63209,7 @@
         </is>
       </c>
       <c r="Z411" t="n">
-        <v>0.7542017609190238</v>
+        <v>0.7542017609190236</v>
       </c>
       <c r="AA411" t="inlineStr">
         <is>
@@ -63247,12 +63247,12 @@
       <c r="AJ411" t="inlineStr"/>
       <c r="AK411" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL411" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM411" t="inlineStr">
@@ -63397,12 +63397,12 @@
       <c r="AJ412" t="inlineStr"/>
       <c r="AK412" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL412" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM412" t="inlineStr">
@@ -63551,12 +63551,12 @@
       <c r="AJ413" t="inlineStr"/>
       <c r="AK413" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL413" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM413" t="inlineStr">
@@ -63705,12 +63705,12 @@
       <c r="AJ414" t="inlineStr"/>
       <c r="AK414" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL414" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM414" t="inlineStr">
@@ -63859,12 +63859,12 @@
       <c r="AJ415" t="inlineStr"/>
       <c r="AK415" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL415" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM415" t="inlineStr">
@@ -64009,12 +64009,12 @@
       <c r="AJ416" t="inlineStr"/>
       <c r="AK416" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL416" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM416" t="inlineStr">
@@ -64159,12 +64159,12 @@
       <c r="AJ417" t="inlineStr"/>
       <c r="AK417" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL417" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM417" t="inlineStr">
@@ -64271,7 +64271,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>0.6554114036115553</v>
+        <v>0.6554114036115554</v>
       </c>
       <c r="AA418" t="inlineStr">
         <is>
@@ -64309,12 +64309,12 @@
       <c r="AJ418" t="inlineStr"/>
       <c r="AK418" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL418" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM418" t="inlineStr">
@@ -64459,12 +64459,12 @@
       <c r="AJ419" t="inlineStr"/>
       <c r="AK419" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL419" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM419" t="inlineStr">
@@ -64571,7 +64571,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>0.6959979038548444</v>
+        <v>0.6959979038548445</v>
       </c>
       <c r="AA420" t="inlineStr">
         <is>
@@ -64609,12 +64609,12 @@
       <c r="AJ420" t="inlineStr"/>
       <c r="AK420" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL420" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM420" t="inlineStr">
@@ -64759,12 +64759,12 @@
       <c r="AJ421" t="inlineStr"/>
       <c r="AK421" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL421" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM421" t="inlineStr">
@@ -64909,12 +64909,12 @@
       <c r="AJ422" t="inlineStr"/>
       <c r="AK422" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL422" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM422" t="inlineStr">
@@ -65021,7 +65021,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>0.7308020418683012</v>
+        <v>0.7308020418683013</v>
       </c>
       <c r="AA423" t="inlineStr">
         <is>
@@ -65059,12 +65059,12 @@
       <c r="AJ423" t="inlineStr"/>
       <c r="AK423" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL423" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM423" t="inlineStr">
@@ -65209,12 +65209,12 @@
       <c r="AJ424" t="inlineStr"/>
       <c r="AK424" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL424" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM424" t="inlineStr">
@@ -65363,12 +65363,12 @@
       <c r="AJ425" t="inlineStr"/>
       <c r="AK425" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL425" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM425" t="inlineStr">
@@ -65517,12 +65517,12 @@
       <c r="AJ426" t="inlineStr"/>
       <c r="AK426" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL426" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM426" t="inlineStr">
@@ -65671,12 +65671,12 @@
       <c r="AJ427" t="inlineStr"/>
       <c r="AK427" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL427" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM427" t="inlineStr">
@@ -65825,12 +65825,12 @@
       <c r="AJ428" t="inlineStr"/>
       <c r="AK428" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL428" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM428" t="inlineStr">
@@ -65979,12 +65979,12 @@
       <c r="AJ429" t="inlineStr"/>
       <c r="AK429" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL429" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM429" t="inlineStr">
@@ -66133,12 +66133,12 @@
       <c r="AJ430" t="inlineStr"/>
       <c r="AK430" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL430" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM430" t="inlineStr">
@@ -66287,12 +66287,12 @@
       <c r="AJ431" t="inlineStr"/>
       <c r="AK431" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL431" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM431" t="inlineStr">
@@ -66441,12 +66441,12 @@
       <c r="AJ432" t="inlineStr"/>
       <c r="AK432" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL432" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM432" t="inlineStr">
@@ -66595,12 +66595,12 @@
       <c r="AJ433" t="inlineStr"/>
       <c r="AK433" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL433" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM433" t="inlineStr">
@@ -66749,12 +66749,12 @@
       <c r="AJ434" t="inlineStr"/>
       <c r="AK434" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL434" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM434" t="inlineStr">
@@ -66903,12 +66903,12 @@
       <c r="AJ435" t="inlineStr"/>
       <c r="AK435" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL435" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM435" t="inlineStr">
@@ -67057,12 +67057,12 @@
       <c r="AJ436" t="inlineStr"/>
       <c r="AK436" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL436" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM436" t="inlineStr">
@@ -67211,12 +67211,12 @@
       <c r="AJ437" t="inlineStr"/>
       <c r="AK437" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL437" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM437" t="inlineStr">
@@ -67365,12 +67365,12 @@
       <c r="AJ438" t="inlineStr"/>
       <c r="AK438" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL438" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM438" t="inlineStr">
@@ -67519,12 +67519,12 @@
       <c r="AJ439" t="inlineStr"/>
       <c r="AK439" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL439" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM439" t="inlineStr">
@@ -67673,12 +67673,12 @@
       <c r="AJ440" t="inlineStr"/>
       <c r="AK440" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL440" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM440" t="inlineStr">
@@ -67827,12 +67827,12 @@
       <c r="AJ441" t="inlineStr"/>
       <c r="AK441" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL441" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM441" t="inlineStr">
@@ -67977,12 +67977,12 @@
       <c r="AJ442" t="inlineStr"/>
       <c r="AK442" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL442" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM442" t="inlineStr">
@@ -68127,12 +68127,12 @@
       <c r="AJ443" t="inlineStr"/>
       <c r="AK443" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL443" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM443" t="inlineStr">
@@ -68277,12 +68277,12 @@
       <c r="AJ444" t="inlineStr"/>
       <c r="AK444" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL444" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM444" t="inlineStr">
@@ -68427,12 +68427,12 @@
       <c r="AJ445" t="inlineStr"/>
       <c r="AK445" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL445" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM445" t="inlineStr">
@@ -68577,12 +68577,12 @@
       <c r="AJ446" t="inlineStr"/>
       <c r="AK446" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL446" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM446" t="inlineStr">
@@ -68727,12 +68727,12 @@
       <c r="AJ447" t="inlineStr"/>
       <c r="AK447" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL447" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM447" t="inlineStr">
@@ -68877,12 +68877,12 @@
       <c r="AJ448" t="inlineStr"/>
       <c r="AK448" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL448" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM448" t="inlineStr">
@@ -69027,12 +69027,12 @@
       <c r="AJ449" t="inlineStr"/>
       <c r="AK449" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL449" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM449" t="inlineStr">
@@ -69139,7 +69139,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>0.6809123048060441</v>
+        <v>0.680912304806044</v>
       </c>
       <c r="AA450" t="inlineStr">
         <is>
@@ -69177,12 +69177,12 @@
       <c r="AJ450" t="inlineStr"/>
       <c r="AK450" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL450" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM450" t="inlineStr">
@@ -69327,12 +69327,12 @@
       <c r="AJ451" t="inlineStr"/>
       <c r="AK451" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL451" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM451" t="inlineStr">
@@ -69439,7 +69439,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>0.7105267520661097</v>
+        <v>0.7105267520661096</v>
       </c>
       <c r="AA452" t="inlineStr">
         <is>
@@ -69477,12 +69477,12 @@
       <c r="AJ452" t="inlineStr"/>
       <c r="AK452" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL452" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM452" t="inlineStr">
@@ -69627,12 +69627,12 @@
       <c r="AJ453" t="inlineStr"/>
       <c r="AK453" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL453" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM453" t="inlineStr">
@@ -69781,12 +69781,12 @@
       <c r="AJ454" t="inlineStr"/>
       <c r="AK454" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL454" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM454" t="inlineStr">
@@ -69935,12 +69935,12 @@
       <c r="AJ455" t="inlineStr"/>
       <c r="AK455" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL455" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM455" t="inlineStr">
@@ -70089,12 +70089,12 @@
       <c r="AJ456" t="inlineStr"/>
       <c r="AK456" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL456" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM456" t="inlineStr">
@@ -70205,7 +70205,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>0.7167529319384154</v>
+        <v>0.7167529319384156</v>
       </c>
       <c r="AA457" t="inlineStr">
         <is>
@@ -70243,12 +70243,12 @@
       <c r="AJ457" t="inlineStr"/>
       <c r="AK457" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL457" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM457" t="inlineStr">
@@ -70397,12 +70397,12 @@
       <c r="AJ458" t="inlineStr"/>
       <c r="AK458" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL458" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM458" t="inlineStr">
@@ -70551,12 +70551,12 @@
       <c r="AJ459" t="inlineStr"/>
       <c r="AK459" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL459" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM459" t="inlineStr">
@@ -70667,7 +70667,7 @@
         </is>
       </c>
       <c r="Z460" t="n">
-        <v>0.7056396513617686</v>
+        <v>0.7056396513617685</v>
       </c>
       <c r="AA460" t="inlineStr">
         <is>
@@ -70705,12 +70705,12 @@
       <c r="AJ460" t="inlineStr"/>
       <c r="AK460" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL460" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM460" t="inlineStr">
@@ -70859,12 +70859,12 @@
       <c r="AJ461" t="inlineStr"/>
       <c r="AK461" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL461" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM461" t="inlineStr">
@@ -71013,12 +71013,12 @@
       <c r="AJ462" t="inlineStr"/>
       <c r="AK462" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL462" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM462" t="inlineStr">
@@ -71167,12 +71167,12 @@
       <c r="AJ463" t="inlineStr"/>
       <c r="AK463" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL463" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM463" t="inlineStr">
@@ -71321,12 +71321,12 @@
       <c r="AJ464" t="inlineStr"/>
       <c r="AK464" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL464" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM464" t="inlineStr">
@@ -71437,7 +71437,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>0.6474675344349394</v>
+        <v>0.6474675344349393</v>
       </c>
       <c r="AA465" t="inlineStr">
         <is>
@@ -71475,12 +71475,12 @@
       <c r="AJ465" t="inlineStr"/>
       <c r="AK465" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL465" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM465" t="inlineStr">
@@ -71629,12 +71629,12 @@
       <c r="AJ466" t="inlineStr"/>
       <c r="AK466" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL466" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM466" t="inlineStr">
@@ -71779,12 +71779,12 @@
       <c r="AJ467" t="inlineStr"/>
       <c r="AK467" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL467" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM467" t="inlineStr">
@@ -71933,12 +71933,12 @@
       <c r="AJ468" t="inlineStr"/>
       <c r="AK468" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL468" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM468" t="inlineStr">
@@ -72049,7 +72049,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>0.5639265782050669</v>
+        <v>0.563926578205067</v>
       </c>
       <c r="AA469" t="inlineStr">
         <is>
@@ -72087,12 +72087,12 @@
       <c r="AJ469" t="inlineStr"/>
       <c r="AK469" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL469" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM469" t="inlineStr">
@@ -72241,12 +72241,12 @@
       <c r="AJ470" t="inlineStr"/>
       <c r="AK470" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL470" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM470" t="inlineStr">
@@ -72395,12 +72395,12 @@
       <c r="AJ471" t="inlineStr"/>
       <c r="AK471" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL471" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM471" t="inlineStr">
@@ -72549,12 +72549,12 @@
       <c r="AJ472" t="inlineStr"/>
       <c r="AK472" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL472" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM472" t="inlineStr">
@@ -72665,7 +72665,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>0.631088915270508</v>
+        <v>0.6310889152705079</v>
       </c>
       <c r="AA473" t="inlineStr">
         <is>
@@ -72703,12 +72703,12 @@
       <c r="AJ473" t="inlineStr"/>
       <c r="AK473" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL473" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM473" t="inlineStr">
@@ -72853,12 +72853,12 @@
       <c r="AJ474" t="inlineStr"/>
       <c r="AK474" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL474" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM474" t="inlineStr">
@@ -73003,12 +73003,12 @@
       <c r="AJ475" t="inlineStr"/>
       <c r="AK475" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL475" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM475" t="inlineStr">
@@ -73153,12 +73153,12 @@
       <c r="AJ476" t="inlineStr"/>
       <c r="AK476" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL476" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM476" t="inlineStr">
@@ -73303,12 +73303,12 @@
       <c r="AJ477" t="inlineStr"/>
       <c r="AK477" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL477" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM477" t="inlineStr">
@@ -73453,12 +73453,12 @@
       <c r="AJ478" t="inlineStr"/>
       <c r="AK478" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL478" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM478" t="inlineStr">
@@ -73603,12 +73603,12 @@
       <c r="AJ479" t="inlineStr"/>
       <c r="AK479" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL479" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM479" t="inlineStr">
@@ -73753,12 +73753,12 @@
       <c r="AJ480" t="inlineStr"/>
       <c r="AK480" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL480" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM480" t="inlineStr">
@@ -73903,12 +73903,12 @@
       <c r="AJ481" t="inlineStr"/>
       <c r="AK481" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL481" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM481" t="inlineStr">
@@ -74053,12 +74053,12 @@
       <c r="AJ482" t="inlineStr"/>
       <c r="AK482" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL482" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM482" t="inlineStr">
@@ -74203,12 +74203,12 @@
       <c r="AJ483" t="inlineStr"/>
       <c r="AK483" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL483" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM483" t="inlineStr">
@@ -74353,12 +74353,12 @@
       <c r="AJ484" t="inlineStr"/>
       <c r="AK484" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL484" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM484" t="inlineStr">
@@ -74503,12 +74503,12 @@
       <c r="AJ485" t="inlineStr"/>
       <c r="AK485" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL485" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM485" t="inlineStr">
@@ -74653,12 +74653,12 @@
       <c r="AJ486" t="inlineStr"/>
       <c r="AK486" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL486" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM486" t="inlineStr">
@@ -74803,12 +74803,12 @@
       <c r="AJ487" t="inlineStr"/>
       <c r="AK487" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL487" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM487" t="inlineStr">
@@ -74953,12 +74953,12 @@
       <c r="AJ488" t="inlineStr"/>
       <c r="AK488" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL488" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM488" t="inlineStr">
@@ -75103,12 +75103,12 @@
       <c r="AJ489" t="inlineStr"/>
       <c r="AK489" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL489" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM489" t="inlineStr">
@@ -75253,12 +75253,12 @@
       <c r="AJ490" t="inlineStr"/>
       <c r="AK490" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL490" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM490" t="inlineStr">
@@ -75403,12 +75403,12 @@
       <c r="AJ491" t="inlineStr"/>
       <c r="AK491" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL491" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM491" t="inlineStr">
@@ -75553,12 +75553,12 @@
       <c r="AJ492" t="inlineStr"/>
       <c r="AK492" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL492" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM492" t="inlineStr">
@@ -75665,7 +75665,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>0.6225180016422348</v>
+        <v>0.6225180016422349</v>
       </c>
       <c r="AA493" t="inlineStr">
         <is>
@@ -75703,12 +75703,12 @@
       <c r="AJ493" t="inlineStr"/>
       <c r="AK493" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL493" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM493" t="inlineStr">
@@ -75853,12 +75853,12 @@
       <c r="AJ494" t="inlineStr"/>
       <c r="AK494" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL494" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM494" t="inlineStr">
@@ -76003,12 +76003,12 @@
       <c r="AJ495" t="inlineStr"/>
       <c r="AK495" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL495" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM495" t="inlineStr">
@@ -76157,12 +76157,12 @@
       <c r="AJ496" t="inlineStr"/>
       <c r="AK496" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL496" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM496" t="inlineStr">
@@ -76311,12 +76311,12 @@
       <c r="AJ497" t="inlineStr"/>
       <c r="AK497" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL497" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM497" t="inlineStr">
@@ -76465,12 +76465,12 @@
       <c r="AJ498" t="inlineStr"/>
       <c r="AK498" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL498" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM498" t="inlineStr">
@@ -76619,12 +76619,12 @@
       <c r="AJ499" t="inlineStr"/>
       <c r="AK499" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL499" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM499" t="inlineStr">
@@ -76773,12 +76773,12 @@
       <c r="AJ500" t="inlineStr"/>
       <c r="AK500" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL500" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM500" t="inlineStr">
@@ -76927,12 +76927,12 @@
       <c r="AJ501" t="inlineStr"/>
       <c r="AK501" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL501" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM501" t="inlineStr">
@@ -77043,7 +77043,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>0.7406142778841094</v>
+        <v>0.7406142778841095</v>
       </c>
       <c r="AA502" t="inlineStr">
         <is>
@@ -77081,12 +77081,12 @@
       <c r="AJ502" t="inlineStr"/>
       <c r="AK502" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL502" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM502" t="inlineStr">
@@ -77235,12 +77235,12 @@
       <c r="AJ503" t="inlineStr"/>
       <c r="AK503" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL503" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM503" t="inlineStr">
@@ -77389,12 +77389,12 @@
       <c r="AJ504" t="inlineStr"/>
       <c r="AK504" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL504" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM504" t="inlineStr">
@@ -77543,12 +77543,12 @@
       <c r="AJ505" t="inlineStr"/>
       <c r="AK505" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL505" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM505" t="inlineStr">
@@ -77697,12 +77697,12 @@
       <c r="AJ506" t="inlineStr"/>
       <c r="AK506" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL506" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM506" t="inlineStr">
@@ -77851,12 +77851,12 @@
       <c r="AJ507" t="inlineStr"/>
       <c r="AK507" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL507" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM507" t="inlineStr">
@@ -78005,12 +78005,12 @@
       <c r="AJ508" t="inlineStr"/>
       <c r="AK508" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL508" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM508" t="inlineStr">
@@ -78159,12 +78159,12 @@
       <c r="AJ509" t="inlineStr"/>
       <c r="AK509" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL509" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM509" t="inlineStr">
@@ -78313,12 +78313,12 @@
       <c r="AJ510" t="inlineStr"/>
       <c r="AK510" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL510" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM510" t="inlineStr">
@@ -78467,12 +78467,12 @@
       <c r="AJ511" t="inlineStr"/>
       <c r="AK511" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL511" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM511" t="inlineStr">
@@ -78621,12 +78621,12 @@
       <c r="AJ512" t="inlineStr"/>
       <c r="AK512" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL512" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM512" t="inlineStr">
@@ -78775,12 +78775,12 @@
       <c r="AJ513" t="inlineStr"/>
       <c r="AK513" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL513" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM513" t="inlineStr">
@@ -78891,7 +78891,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>0.6238654553358168</v>
+        <v>0.6238654553358167</v>
       </c>
       <c r="AA514" t="inlineStr">
         <is>
@@ -78929,12 +78929,12 @@
       <c r="AJ514" t="inlineStr"/>
       <c r="AK514" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL514" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM514" t="inlineStr">
@@ -79079,12 +79079,12 @@
       <c r="AJ515" t="inlineStr"/>
       <c r="AK515" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL515" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM515" t="inlineStr">
@@ -79229,12 +79229,12 @@
       <c r="AJ516" t="inlineStr"/>
       <c r="AK516" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL516" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM516" t="inlineStr">
@@ -79379,12 +79379,12 @@
       <c r="AJ517" t="inlineStr"/>
       <c r="AK517" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL517" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM517" t="inlineStr">
@@ -79529,12 +79529,12 @@
       <c r="AJ518" t="inlineStr"/>
       <c r="AK518" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL518" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM518" t="inlineStr">
@@ -79679,12 +79679,12 @@
       <c r="AJ519" t="inlineStr"/>
       <c r="AK519" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL519" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM519" t="inlineStr">
@@ -79791,7 +79791,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>0.6992427404247544</v>
+        <v>0.6992427404247543</v>
       </c>
       <c r="AA520" t="inlineStr">
         <is>
@@ -79829,12 +79829,12 @@
       <c r="AJ520" t="inlineStr"/>
       <c r="AK520" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL520" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM520" t="inlineStr">
@@ -79979,12 +79979,12 @@
       <c r="AJ521" t="inlineStr"/>
       <c r="AK521" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL521" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM521" t="inlineStr">
@@ -80129,12 +80129,12 @@
       <c r="AJ522" t="inlineStr"/>
       <c r="AK522" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL522" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM522" t="inlineStr">
@@ -80279,12 +80279,12 @@
       <c r="AJ523" t="inlineStr"/>
       <c r="AK523" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL523" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM523" t="inlineStr">
@@ -80429,12 +80429,12 @@
       <c r="AJ524" t="inlineStr"/>
       <c r="AK524" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL524" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM524" t="inlineStr">
@@ -80579,12 +80579,12 @@
       <c r="AJ525" t="inlineStr"/>
       <c r="AK525" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL525" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM525" t="inlineStr">
@@ -80729,12 +80729,12 @@
       <c r="AJ526" t="inlineStr"/>
       <c r="AK526" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL526" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM526" t="inlineStr">
@@ -80841,7 +80841,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>0.6969296857018888</v>
+        <v>0.6969296857018887</v>
       </c>
       <c r="AA527" t="inlineStr">
         <is>
@@ -80879,12 +80879,12 @@
       <c r="AJ527" t="inlineStr"/>
       <c r="AK527" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL527" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM527" t="inlineStr">
@@ -80991,7 +80991,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>0.6679367200725025</v>
+        <v>0.6679367200725024</v>
       </c>
       <c r="AA528" t="inlineStr">
         <is>
@@ -81029,12 +81029,12 @@
       <c r="AJ528" t="inlineStr"/>
       <c r="AK528" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL528" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM528" t="inlineStr">
@@ -81179,12 +81179,12 @@
       <c r="AJ529" t="inlineStr"/>
       <c r="AK529" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL529" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM529" t="inlineStr">
@@ -81291,7 +81291,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>0.7121606629770859</v>
+        <v>0.712160662977086</v>
       </c>
       <c r="AA530" t="inlineStr">
         <is>
@@ -81329,12 +81329,12 @@
       <c r="AJ530" t="inlineStr"/>
       <c r="AK530" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="AL530" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="AM530" t="inlineStr">
